--- a/OrangeHRM/src/main/resources/TestData.xlsx
+++ b/OrangeHRM/src/main/resources/TestData.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java Programming\TestNG\Selenium\ProjectOrangeHRM\OrangeHRM\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\My PC\Desktop\Project\OrangeHRM\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BD46E47-2651-4E90-9F65-807480E8DB8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C6D762-6A3E-4EC0-8EC5-9BD196897A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{18ED8837-B8CF-4EA3-982B-FD1470EB4EED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{18ED8837-B8CF-4EA3-982B-FD1470EB4EED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>username</t>
   </si>
@@ -53,6 +54,15 @@
   </si>
   <si>
     <t>123456</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>manda akhil user</t>
+  </si>
+  <si>
+    <t>Timesheet for manda user</t>
   </si>
 </sst>
 </file>
@@ -477,4 +487,42 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4577810-4CC4-43E7-88B5-413E24D9F557}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>